--- a/docs/sprint3/test-cases.xlsx
+++ b/docs/sprint3/test-cases.xlsx
@@ -444,19 +444,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
@@ -546,7 +546,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1. Відкрити https://opensource-demo.orangehrmlive.com.
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
 2. У полі Username ввести Admin.
 3. У полі Password ввести admin123.
 4. Натиснути Login.</t>
@@ -556,7 +556,7 @@
         <is>
           <t>1. Показано сторінку входу з полями Username, Password і кнопкою Login.
 2–3. Значення введено, повідомлень про помилку немає.
-4. Відкрито Dashboard; ліворуч — бічне меню модулів за роллю.</t>
+4. Відкрито Dashboard за адресою /dashboard/index; ліворуч — бічне меню модулів.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1. Відкрити demo.
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), відкрити сторінку входу.
 2. Username = Admin.
 3. Password = wrongpass1.
 4. Натиснути Login.</t>
@@ -621,7 +621,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Над формою з'являється червоне повідомлення «Wrong username or password» (за GUI-20); користувач лишається на сторінці входу.</t>
+          <t>Над формою з'являється червоне повідомлення «Wrong username or password» (за GUI-20); користувач лишається на сторінці входу /auth/login.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1. Відкрити demo.
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), відкрити сторінку входу.
 2. Поля Username і Password лишити порожніми.
 3. Натиснути Login.</t>
         </is>
@@ -737,23 +737,24 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Вхід як Admin. Існує працівник для прив'язки. Admin → User Management → Add User.</t>
+          <t>Працівник «Peter Mac Anderson» існує у PIM. Користувача з ім'ям teame.user04 ще немає.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1. Role = ESS.
-2. Employee Name = (існуючий працівник).
-3. Status = Enabled.
-4. Username = test.user01 (5–40 символів, унікальний).
-5. Password = Testuser1! (8–64, велика+мала+цифра+спецсимвол).
-6. Confirm Password = Testuser1!.
-7. Save.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Admin → User Management → Add User.
+3. User Role = ESS.
+4. Employee Name = Peter Mac Anderson.
+5. Status = Enabled.
+6. Username = teame.user04.
+7. Password = Teampass4! ; Confirm Password = Teampass4! (8–64, велика+мала+цифра+спецсимвол).
+8. Save.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Користувача збережено; у правому нижньому куті — «Successfully Saved»; запис з'являється у списку користувачів.</t>
+          <t>Користувача збережено; у правому нижньому куті — «Successfully Saved»; запис teame.user04 (ESS, Peter Anderson, Enabled) з'являється у списку System Users.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -805,16 +806,18 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Admin → User Management → Add User, заповнено всі поля крім пароля.</t>
+          <t>Admin → User Management → Add User; Role=ESS, Employee=Peter Mac Anderson, Status=Enabled, Username=teame.pw&lt;N&gt; (унікальний для рядка).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Для кожного рядка ввести пароль у Password і Confirm, натиснути Save і зафіксувати реакцію:
-(1) «Test1!a» — 7 символів;
-(2) «Testuser1» — немає спецсимволу;
-(3) «testuser1!» — немає великої літери;
-(4) «Testuser1!» — повний набір.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Admin → User Management → Add User, заповнити Role=ESS, Employee=Peter Mac Anderson, Status=Enabled.
+3. Для кожного рядка ввести Username teame.pw1…pw4, пароль у Password і Confirm, натиснути Save:
+ (1) «Test1!a» — 7 символів;
+ (2) «Teampass1» — немає спецсимволу;
+ (3) «teampass1!» — немає великої літери;
+ (4) «Teampass1!» — повний набір.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -823,7 +826,7 @@
 (1) відхилено (замало символів);
 (2) відхилено (немає спецсимволу);
 (3) відхилено (немає великої літери);
-(4) прийнято.</t>
+(4) прийнято — «Successfully Saved».</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -875,23 +878,24 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Вхід як Admin. PIM → Employee List. У базі є ≥2 працівники.</t>
+          <t>У PIM є працівник «Amelia Brown». Користувач — Admin.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1. Відкрити Employee List.
-2. У фільтрі Employee Name ввести частину імені наявного працівника, Search.
-3. Reset.
-4. Клацнути заголовок стовпця для сортування.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. PIM → Employee List.
+3. У фільтрі Employee Name ввести «Amelia», Search.
+4. Reset.
+5. Клацнути заголовок стовпця «First (&amp; Middle) Name» для сортування.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Над таблицею показано «(N) Records Found».
-2. У списку лише відповідні записи.
-3. Reset повертає повний список.
-4. Рядки сортуються за зростанням/спаданням.</t>
+3. У списку лише записи з ім'ям Amelia (зокрема Amelia Brown).
+4. Reset повертає повний список.
+5. Рядки сортуються за зростанням/спаданням.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -938,25 +942,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Додавання працівника та перевірка поля РНОКПП</t>
+          <t>Додавання працівника та перевірка РНОКПП</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Вхід як Admin. PIM → Add Employee.</t>
+          <t>Користувач — Admin. PIM → Add Employee.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1. Ввести First Name, Last Name.
-2. Лишити запропонований Employee Id.
-3. Знайти поле для РНОКПП (податковий номер) серед полів форми/профілю.
-4. Save.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. PIM → Add Employee.
+3. First Name = Тест, Last Name = Працівник07.
+4. Лишити запропонований Employee Id.
+5. Серед полів форми і вкладок профілю знайти поле для РНОКПП (податковий номер).
+6. Ввести РНОКПП «1234567890» (10 цифр) і Save.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>За SRS 1.1 (F-50) під час збереження має виконуватись локальна перевірка формату РНОКПП (рівно 10 цифр). Очікується наявність відповідного поля і валідація.</t>
+          <t>За SRS 1.1 (F-50/BL-80): на формі є поле РНОКПП; під час збереження перевіряється формат — рівно 10 цифр приймається, інакше показується повідомлення про помилку формату і запис не зберігається. Для «1234567890» — запис зберігається, профіль відкривається.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -981,7 +987,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1008,22 +1014,24 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PIM → Add Employee або вкладка профілю з полем податкового номера.</t>
+          <t>Форма Add Employee або вкладка профілю з полем РНОКПП (див. TC-007).</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Для кожного рядка ввести значення у поле РНОКПП і зберегти:
-(1) «123456789» — 9 цифр;
-(2) «1234567890» — 10 цифр;
-(3) «12345678901» — 11 цифр;
-(4) «12345abcde» — літери.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. PIM → Add Employee; First Name = Тест, Last Name = РНОКПП&lt;N&gt;.
+3. Для кожного рядка ввести значення у поле РНОКПП і Save:
+ (1) «123456789» — 9 цифр;
+ (2) «1234567890» — 10 цифр;
+ (3) «12345678901» — 11 цифр;
+ (4) «12345abcde» — літери.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>За BL-80 isValidTaxId приймає рівно 10 цифр. Очікування:
-(1) відхилено; (2) прийнято; (3) відхилено; (4) відхилено (не цифри).</t>
+(1) відхилено (замало цифр); (2) прийнято; (3) відхилено (забагато); (4) відхилено (не цифри).</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1048,7 +1056,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1075,21 +1083,21 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Вхід як Admin; обрано працівника у PIM.</t>
+          <t>У PIM є працівник «Amelia Brown». Користувач — Admin.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1. Відкрити профіль → переглянути вкладки Personal Details, Contact Details, Job, Salary тощо.
-2. Відкрити My Info.
-3. Спробувати редагувати контактні дані та, окремо, Job/Salary.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. PIM → Employee List → відкрити профіль Amelia Brown.
+3. Переглянути вкладки Personal Details, Contact Details, Job, Salary.
+4. My Info → спробувати редагувати контактні дані, потім відкрити Job/Salary.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1. Присутні вкладки за F-60.
-2. My Info показує власний профіль.
-3. У My Info редагуються лише контактні дані; службові (Job/Salary) — недоступні для редагування працівником.</t>
+          <t>3. Присутні вкладки за F-60.
+4. У My Info редагуються лише контактні дані; службові (Job/Salary) недоступні для редагування працівником.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1141,22 +1149,24 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Вхід як Admin (роль через Admin). Для типу відпустки додано ліміт (entitlement). Leave → Apply.</t>
+          <t>Для John Doe (Admin) у Leave → Entitlements додано ліміт CAN - Vacation 10 днів на 2026 (див. TC-015).</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1. Leave Type = (тип з лімітом).
-2. From Date = пн, To Date = пт того ж тижня.
-3. Partial Days = None.
-4. Переглянути Leave Balance.
-5. Apply.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Leave → Apply.
+3. Leave Type = CAN - Vacation.
+4. From Date = 2026-19-10 (пн), To Date = 2026-23-10 (пт).
+5. Partial Days = None.
+6. Переглянути Leave Balance.
+7. Apply.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3–4. Під списком показано Leave Balance у форматі «N.NN Day(s)».
-5. Заявка збережена зі статусом Pending Approval; тривалість = 5 робочих днів (вихідні не враховано, за BL-30).</t>
+          <t>6. Під списком показано Leave Balance «10.00 Day(s)».
+7. Заявка збережена зі статусом Pending Approval; тривалість = 5 робочих днів (сб-нд не враховано, за BL-30).</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1181,7 +1191,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1208,19 +1218,21 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Leave → Apply; обрано тип відпустки.</t>
+          <t>Для John Doe є ліміт CAN - Vacation 10 днів (див. TC-015). Leave → Apply.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1. From Date = 20-е число, To Date = 18-е (раніше за початок) → Apply.
-2. Повернутись; обрати діапазон, що перевищує баланс → Apply.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Leave → Apply; Leave Type = CAN - Vacation.
+3. From Date = 2026-23-10, To Date = 2026-20-10 (раніше за початок) → Apply.
+4. Повторити: From Date = 2026-02-11, To Date = 2026-20-11 (15 робочих днів &gt; баланс 10) → Apply.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Під полем To Date показано повідомлення про помилку; заявка не зберігається.
-2. Показано «Balance not sufficient»; заявка не зберігається.</t>
+          <t>3. Під полем To Date показано повідомлення про помилку («To date should be after from date»); заявка не зберігається.
+4. Показано «Balance not sufficient»; заявка не зберігається.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1245,7 +1257,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1272,20 +1284,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Leave → Apply; тип з достатнім лімітом.</t>
+          <t>Для John Doe є ліміт CAN - Vacation 10 днів (див. TC-015). Leave → Apply.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Для кожного рядка обрати дати і зафіксувати обчислену тривалість:
-(1) пн–пт (07.09–11.09.2026);
-(2) один день (09.09–09.09);
-(3) пт–пн через вихідні (11.09–14.09).</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Leave → Apply; Leave Type = CAN - Vacation.
+3. Для кожного рядка обрати From/To і зафіксувати обчислену тривалість (Leave Balance / Duration):
+ (1) 2026-19-10 – 2026-23-10 (пн–пт);
+ (2) 2026-20-10 – 2026-20-10 (один день);
+ (3) 2026-23-10 – 2026-26-10 (пт–пн через вихідні).</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>За BL-30 (робочі дні, вихідні не враховуються):
+          <t>За BL-30 (робочі дні, сб-нд не враховуються):
 (1) 5; (2) 1; (3) 2 (пт і пн; сб-нд не рахуються).</t>
         </is>
       </c>
@@ -1328,31 +1342,33 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>F-80</t>
+          <t>F-80 / F-70</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Перегляд і скасування власної заявки</t>
+          <t>Створення, перегляд і скасування власної заявки</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Є заявка у статусі Pending Approval. Leave → My Leave.</t>
+          <t>Для John Doe є ліміт CAN - Vacation 10 днів (див. TC-015).</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1. Відкрити My Leave за поточний період.
-2. Застосувати фільтр за статусом Pending Approval.
-3. Для заявки натиснути Cancel.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Leave → Apply: Leave Type = CAN - Vacation, From = 2026-28-10, To = 2026-28-10, Apply (створює заявку Pending Approval).
+3. Leave → My Leave за поточний період.
+4. Фільтр за статусом Pending Approval.
+5. Для створеної заявки натиснути Cancel.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1. Показано власні заявки з датами, типом, тривалістю, статусом.
-2. Відфільтровано лише Pending.
-3. Заявку скасовано (статус Cancelled), поки це дозволено.</t>
+          <t>2. Заявку створено (Pending Approval).
+3–4. У списку показано власну заявку з датою, типом, тривалістю, статусом; відфільтровано лише Pending.
+5. Заявку скасовано — статус Cancelled.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1377,7 +1393,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1399,27 +1415,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Погодження/відхилення заявки та нагадування</t>
+          <t>Погодження і відхилення заявок на відпустку</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Є заявка Pending Approval. Leave → Leave List (роль керівника через Admin).</t>
+          <t>Для John Doe є ліміт CAN - Vacation 10 днів (див. TC-015).</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1. Відкрити Leave List, знайти заявку Pending Approval.
-2. Approve з коментарем.
-3. Для іншої заявки — Reject з коментарем.
-4. Перевірити, чи є нагадування керівнику про заявку, що очікує понад 24 години (за F-90).</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Leave → Apply: CAN - Vacation, 2026-29-10 – 2026-29-10, Apply (заявка А, Pending).
+3. Leave → Apply: CAN - Vacation, 2026-30-10 – 2026-30-10, Apply (заявка Б, Pending).
+4. Leave → Leave List, знайти заявки Pending Approval.
+5. Для заявки А — Approve з коментарем «Погоджено».
+6. Для заявки Б — Reject з коментарем «Відхилено».
+7. Перевірити, чи є нагадування керівнику про заявку, що очікує погодження понад 24 години (F-90).</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2. Заявка → Scheduled.
-3. Інша → Rejected.
-4. За SRS 1.1 (F-90) має бути нагадування в кабінеті системи про заявку, що очікує погодження &gt;24 год.</t>
+          <t>5. Заявка А → Scheduled.
+6. Заявка Б → Rejected.
+7. За SRS 1.1 (F-90) має бути нагадування в кабінеті системи про заявку, що очікує погодження &gt;24 год.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1444,7 +1463,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,26 +1485,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Призначення відпустки і розрахунок балансу</t>
+          <t>Додавання ліміту і призначення відпустки</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Вхід як Admin. Leave → Entitlements (додати ліміт), далі Leave → Assign Leave.</t>
+          <t>У PIM є працівник «Amelia Brown». Користувач — Admin.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1. Entitlements → Add: працівник, тип, період, кількість днів. Save.
-2. Assign Leave: той самий працівник, тип, дати. Assign.
-3. Відкрити баланс працівника.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Leave → Entitlements → Add Leave Entitlement: Employee = Amelia Brown, Leave Type = CAN - Vacation, Leave Period = 2026, Entitlement = 10, Save, Confirm.
+3. Leave → Assign Leave: Employee = Amelia Brown, Leave Type = CAN - Vacation, From = 2026-26-10, To = 2026-27-10, Assign.
+4. Переглянути баланс Amelia Brown (Leave Balance у формі).</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1. Ліміт додано.
-2. Призначену відпустку одразу переведено у Scheduled.
-3. Баланс = ліміт − використані − заплановані; заявки Pending окремо резервують дні (без подвійного віднімання).</t>
+          <t>2. Ліміт 10 днів додано.
+3. Призначену відпустку одразу переведено у статус Scheduled.
+4. Баланс = ліміт − використані − заплановані; заявки Pending окремо резервують дні (без подвійного віднімання).</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1510,7 +1530,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1537,23 +1557,25 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Вхід як Admin. Time → Timesheets → My Timesheets.</t>
+          <t>Користувач — Admin. Time → Timesheets → My Timesheets.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1. Додати рядок «проєкт — вид роботи», ввести години за дні тижня. Save.
-2. Submit.
-3. (Роль керівника) Reject поданий табель.
-4. Повернутись працівником, відредагувати той самий табель і Submit повторно.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Time → Timesheets → My Timesheets.
+3. Додати рядок: Project = (будь-який з довідника), Activity = (будь-яка), ввести по 8 годин у пн–пт. Save.
+4. Submit.
+5. (роль керівника) Reject поданий табель.
+6. Повернутись працівником, відредагувати той самий табель (змінити години) і Submit повторно.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1. Підсумки за день/тиждень пораховано; статус Not Submitted.
-2. Статус Submitted.
-3. Статус Rejected.
-4. Той самий табель відредаговано і знову подано (новий табель не створюється).</t>
+          <t>3. Підсумки за день/тиждень пораховано; статус Not Submitted.
+4. Статус Submitted.
+5. Статус Rejected.
+6. Той самий табель відредаговано і знову подано (новий табель не створюється).</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1605,20 +1627,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Вхід як Admin. Recruitment → Vacancies → Add.</t>
+          <t>Користувач — Admin. У довіднику посад є «QA Lead».</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1. Заповнити назву, посаду, менеджера, кількість позицій, Active.
-2. Save.
-3. Перевірити, де активна вакансія стає видимою (внутрішня сторінка вакансій за SRS 1.1).</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Recruitment → Vacancies → Add.
+3. Vacancy Name = QA Engineer (Team E); Job Title = QA Lead; Hiring Manager = John Doe; Number of Positions = 2; Active = увімкнено.
+4. Save.
+5. Перевірити, де активна вакансія стає видимою (внутрішня сторінка вакансій за SRS 1.1).</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1–2. Вакансію створено; показано у списку; фільтри працюють.
-3. За SRS 1.1 (F-130) активна вакансія публікується на внутрішній сторінці вакансій продукту.</t>
+          <t>3–4. Вакансію створено; показано у списку Vacancies; фільтри працюють.
+5. За SRS 1.1 (F-130) активна вакансія публікується на внутрішній сторінці вакансій продукту (не на зовнішніх ресурсах).</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1643,7 +1667,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1670,19 +1694,21 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Вхід як Admin. Recruitment → Candidates → Add.</t>
+          <t>Користувач — Admin. Recruitment → Candidates → Add.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1. Ввести ім'я, прізвище, вакансію, коректний email (name@mail.com). Save.
-2. Повторити з некоректним email (name@mail) → Save.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Recruitment → Candidates → Add.
+3. First Name = Тест, Last Name = Кандидат18, Email = test18@mail.com (коректний). Save.
+4. Повторити з Email = test18@mail (некоректний) → Save.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Кандидата збережено.
-2. За BL-80 isValidEmail: некоректний формат відхилено з повідомленням; запис не збережено.</t>
+          <t>3. Кандидата збережено.
+4. За BL-80 isValidEmail: некоректний формат відхилено («Expected format: admin@example.com»); запис не збережено.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1734,21 +1760,23 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Leave → Apply; тип з лімітом.</t>
+          <t>Для Amelia Brown є ліміт CAN - Vacation 10 днів (див. TC-015).</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1. Обрати Partial Days = Half Day - Morning. Apply.
-2. Повторити з Partial Days = Specify Time і ввести довільний проміжок (напр. 2 години).
-3. Порівняти обчислену тривалість із кроком 0,5 дня за SRS 1.1.</t>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Leave → Assign Leave: Employee = Amelia Brown, Leave Type = CAN - Vacation, From = 2026-23-10, To = 2026-23-10 (один день).
+3. У полі Duration обрати «Half Day - Morning».
+4. Повторити з Duration = «Specify Time» і ввести проміжок (напр. 09:00–11:00).
+5. Порівняти обчислену тривалість із кроком 0,5 дня за SRS 1.1.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>За SRS 1.1 (F-70/BL-30) часткові дні — крок 0,5 дня.
-1. Пів дня = 0,5 — очікувано.
-2. «Specify Time» не має давати гранулярність дрібнішу за 0,5 дня.</t>
+3. Пів дня = 0,5 — очікувано.
+4. «Specify Time» не має давати гранулярність дрібнішу за 0,5 дня.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1773,10 +1801,77 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TC-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>GUI-30</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Навігація: бічне меню, панель і меню користувача</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Виконано вхід як Admin (TC-001).</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1. Відкрити https://opensource-demo.orangehrmlive.com у Chrome (нова сесія), увійти як Admin / admin123.
+2. Переглянути бічне меню ліворуч.
+3. У полі пошуку над меню ввести «Leave».
+4. Відкрити меню користувача (ім'я вгорі праворуч).</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2. Бічне меню містить пункти Admin, PIM, Leave, Time, Recruitment, My Info, Performance, Dashboard, Directory, Maintenance, Claim, Buzz (за роллю).
+3. Меню фільтрується до пункту Leave.
+4. Меню користувача містить About, Support, Change Password, Logout.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>позитивний</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Злата</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Юлія</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>21.10</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
@@ -1793,12 +1888,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1945,7 +2040,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TC-010, TC-011, TC-012, TC-019</t>
+          <t>TC-010, TC-011, TC-012, TC-013, TC-019</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -2115,17 +2210,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GUI-40</t>
+          <t>GUI-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Позначки «Required»</t>
+          <t>Бічне меню, панель, меню користувача</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>TC-003</t>
+          <t>TC-020</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -2133,17 +2228,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GUI-50</t>
+          <t>GUI-40</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Правила пароля</t>
+          <t>Позначки «Required»</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>TC-004, TC-005</t>
+          <t>TC-003</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -2151,17 +2246,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GUI-60</t>
+          <t>GUI-50</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>«(N) Records Found», сортування</t>
+          <t>Правила пароля</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>TC-006</t>
+          <t>TC-004, TC-005</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -2169,17 +2264,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GUI-70</t>
+          <t>GUI-60</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Форма заявки, баланс, часткові дні</t>
+          <t>«(N) Records Found», сортування</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>TC-010, TC-011, TC-019</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -2187,118 +2282,114 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GUI-80</t>
+          <t>GUI-70</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Оновлення підсумків табеля</t>
+          <t>Форма заявки, баланс, часткові дні</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>TC-016</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>видимо через UI; поріг ≤200 мс — юніт/перф, не на demo</t>
-        </is>
-      </c>
+          <t>TC-010, TC-011, TC-019</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GUI-90</t>
+          <t>GUI-80</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Форма кандидата</t>
+          <t>Оновлення підсумків табеля</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>TC-018</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
+          <t>TC-016</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>видимо через UI; поріг ≤200 мс — юніт/перф, не на demo</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>BL-30</t>
+          <t>GUI-90</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>durationDays (робочі дні)</t>
+          <t>Форма кандидата</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>TC-012</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>правило видно через інтерфейс</t>
-        </is>
-      </c>
+          <t>TC-018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>BL-80</t>
+          <t>BL-30</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>isValidEmail / isValidTaxId</t>
+          <t>durationDays (робочі дні)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>TC-008, TC-018</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>частково через UI</t>
+          <t>правило видно через інтерфейс</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>BL-10..BL-70</t>
+          <t>BL-80</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Розрахунки відпусток/зарплат</t>
+          <t>isValidEmail / isValidTaxId</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TC-008, TC-018</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>не покрито: юніт-тести спринту 4 (немає UI на demo)</t>
+          <t>частково через UI</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>P-10, P-20</t>
+          <t>BL-10..BL-70</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Продуктивність/навантаження</t>
+          <t>Розрахунки відпусток/зарплат</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2308,111 +2399,133 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>не покрито: §2.3 — лише на резерві, не на публічному demo</t>
+          <t>не покрито: юніт-тести спринту 4 (немає UI на demo)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>P-10, P-20</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Правило пароля</t>
+          <t>Продуктивність/навантаження</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>TC-005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>перетин з GUI-50</t>
+          <t>не покрито: §2.3 — лише на резерві, не на публічному demo</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>S-20</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Таймаут сесії 30 хв</t>
+          <t>Правило пароля</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>не покрито цим прогоном: потребує тривалого очікування (окремий тест)</t>
+          <t>перетин з GUI-50</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>U-10</t>
+          <t>S-20</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Позначки обов'язкових полів</t>
+          <t>Таймаут сесії 30 хв</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>TC-003</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>не покрито цим прогоном: потребує тривалого очікування (окремий тест)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>U-20</t>
+          <t>U-10</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Юзабіліті 9/10 за ≤3 хв</t>
+          <t>Позначки обов'язкових полів</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>не покрито: окрема юзабіліті-сесія, не функціональний кейс</t>
-        </is>
-      </c>
+          <t>TC-003</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>U-20</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Юзабіліті 9/10 за ≤3 хв</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>не покрито: окрема юзабіліті-сесія, не функціональний кейс</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>D-10, D-20</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Довідка/документація</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>не покрито: ручний огляд документації, поза прогоном кейсів</t>
         </is>
@@ -2429,13 +2542,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2457,7 +2570,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Зауваження</t>
+          <t>Зауваження (чек-лист §5.3)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -2484,12 +2597,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Крок 1 має починатися з відкриття застосунку — додано URL.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2678,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Дані були неконкретні («існуючий працівник») — підставлено Peter Mac Anderson, teame.user04.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2705,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Додати очікування по кожному рядку таблиці — зроблено</t>
+          <t>Додати очікування по кожному рядку таблиці даних — зроблено.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2619,12 +2732,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Вказати конкретний фільтр (Amelia) — зроблено.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -2641,17 +2754,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Очікуваний результат був нечіткий («очікується наявність») — переписано на перевірюваний стан (10 цифр приймається, інакше помилка).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2781,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2722,17 +2835,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Leave Type і дати без конкретики — підставлено CAN - Vacation, 19–23.10; додано передумову про ліміт.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -2749,17 +2862,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Дати без місяця — додано; баланс конкретизовано (15 днів &gt; 10).</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2894,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Зазначити, чому гранична межа (вихідні) — зроблено</t>
+          <t>Зазначити, чому гранична межа (вихідні) — зроблено.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -2803,17 +2916,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Кейс спирався на наявну Pending-заявку — тепер сам створює її через Apply.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -2830,17 +2943,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Залежність від зовнішньої заявки — кейс створює дві заявки сам; дані задано.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -2857,17 +2970,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Параметри ліміту й призначення конкретизовано (Amelia Brown, 10 днів, дати).</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -2911,17 +3024,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Поля вакансії без значень — підставлено назву, посаду, менеджера, 2 позиції.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
         </is>
       </c>
     </row>
@@ -2965,17 +3078,44 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Уточнено крок через Assign Leave і конкретний проміжок часу.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>так</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TC-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Юлія</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>21.10</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Новий кейс для GUI-30 (меню, панель) — додано за зауваженням про покриття.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
         </is>
       </c>
     </row>
